--- a/tasks/tasks.xlsx
+++ b/tasks/tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ykama\Git-hdir\varia\tasks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C04267-318E-43F2-B17B-E9D004876649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62CDC58F-48F5-4C1C-8BED-A1CA19A9E6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18540" yWindow="2820" windowWidth="26250" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23715" yWindow="3600" windowWidth="26250" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -40,9 +40,6 @@
     <t>Andre arbeidsoppgaver som ikke passer naturlig inn i kategoriene ovenfor.</t>
   </si>
   <si>
-    <t>Statistikk- og analysearbeid</t>
-  </si>
-  <si>
     <t>Tilrettelegging, kvalitetssikring, utarbeidelse og analyse av mottatte data</t>
   </si>
   <si>
@@ -52,14 +49,29 @@
     <t>Publisering og formidling av statistikk, analyser og andre resultater.</t>
   </si>
   <si>
-    <t>Utviklingsarbeid/kompetanseutvikling</t>
-  </si>
-  <si>
     <t>Utvikling av nye løsninger, metoder og systemer/ deltakelse i kurs, opplæring og andre aktiviteter for faglig utvikling.</t>
   </si>
   <si>
+    <t>Svare på henvendelser, feilrettinger, tekniske utfordringer +++</t>
+  </si>
+  <si>
+    <t>Diskusjoner/møter som gir faglig nytte, styrker samarbeid eller bidrar til framdrift i arbeidet.</t>
+  </si>
+  <si>
+    <t>Deltakelse i møter som i mindre grad oppleves å gi faglig nytte eller bidrar til framdrift i arbeidet.</t>
+  </si>
+  <si>
+    <t>task_text</t>
+  </si>
+  <si>
+    <t>Statistikk og analysearbeid</t>
+  </si>
+  <si>
+    <t>Kompetanse og utviklingsarbeid</t>
+  </si>
+  <si>
     <r>
-      <t>Ad hoc-henvendelser/brannslukking</t>
+      <t>Ad hoc-henvendelser og brannslukking</t>
     </r>
     <r>
       <rPr>
@@ -71,25 +83,13 @@
     </r>
   </si>
   <si>
-    <t>Svare på henvendelser, feilrettinger, tekniske utfordringer +++</t>
-  </si>
-  <si>
-    <t>Faglige diskusjoner/møter</t>
-  </si>
-  <si>
-    <t>Diskusjoner/møter som gir faglig nytte, styrker samarbeid eller bidrar til framdrift i arbeidet.</t>
-  </si>
-  <si>
-    <t>Deltakelse i møter/arbeid som oppleves som mindre nyttig</t>
-  </si>
-  <si>
-    <t>Deltakelse i møter som i mindre grad oppleves å gi faglig nytte eller bidrar til framdrift i arbeidet.</t>
-  </si>
-  <si>
-    <t>Koordinering/administrasjon/rapportering</t>
-  </si>
-  <si>
-    <t>task_text</t>
+    <t>Faglige diskusjoner og møter</t>
+  </si>
+  <si>
+    <t>Mindre nyttige møter og arbeid</t>
+  </si>
+  <si>
+    <t>Administrasjon og rapportering</t>
   </si>
 </sst>
 </file>
@@ -480,31 +480,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -517,31 +517,31 @@
     </row>
     <row r="6" spans="1:2" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>1</v>
